--- a/call-list/私立高校_架電リスト_青森県.xlsx
+++ b/call-list/私立高校_架電リスト_青森県.xlsx
@@ -2228,7 +2228,7 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>・「番号の確度」：高＝公式サイト、または2つ以上の情報源で一致／中＝情報サイト1件のみで確認／低・要調査＝特定できず。</t>
+          <t>・「番号の確度」：高＝公式サイト、または2つ以上の情報源で一致／中＝情報サイト1件のみ、または代表番号と断定できず（補足欄参照）／低・要調査＝特定できず。</t>
         </is>
       </c>
     </row>
@@ -2242,14 +2242,14 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>・市区町村で絞り込む場合は、見出し行「所在地（市区町村）」の▼（フィルター）を使用してください。</t>
+          <t>・都道府県や市区町村で絞り込む場合は、見出し行の▼（フィルター）を使用してください。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>・「市区町村別集計」は入力内容に連動して自動で集計されます（学校数の多い順）。</t>
+          <t>・集計シートは入力内容に連動して自動で集計されます。</t>
         </is>
       </c>
     </row>
@@ -2266,14 +2266,14 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・青森県、17校）の貼り付けデータ。並び順は元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・青森県、17校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>・電話番号は元データに記載がないため、2026年10月にWeb検索（学校公式サイト、JS日本の学校、みんなの高校情報、自治体・ハローワーク・道私学協会の資料など）で調査しました。推測による補完はしていません。</t>
+          <t>・電話番号は元データに記載がないため、2026年10月にWeb検索（学校公式サイト、JS日本の学校、みんなの高校情報、自治体・ハローワーク・各道県の私学協会の資料など）で調査しました。推測による補完はしていません。</t>
         </is>
       </c>
     </row>
